--- a/events/LaSeu_2019_WWC/LaSeu_2019_WWC_start.xlsx
+++ b/events/LaSeu_2019_WWC/LaSeu_2019_WWC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W380"/>
+  <dimension ref="A1:AC377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -580,11 +610,6 @@
       <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>F1 TIP</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -633,11 +658,6 @@
       <c r="K3" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>F2 TIP</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -686,11 +706,6 @@
       <c r="K4" t="n">
         <v>3</v>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>F3 TIP</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -769,17 +784,17 @@
           <t>TOLIC Ivan</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>36939</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>39639</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>39671</t>
         </is>
@@ -862,17 +877,17 @@
           <t>DELL'AGOSTINO Giorgio</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>39775</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>75796</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>36551</t>
         </is>
@@ -955,17 +970,17 @@
           <t>FREIRE Manuel</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>37657</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>71117</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>70071</t>
         </is>
@@ -1048,17 +1063,17 @@
           <t>SOSKA Samo</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>82996</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>42277</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>89137</t>
         </is>
@@ -1141,17 +1156,17 @@
           <t>SCHWARZ Ole</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>36679</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>43111</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>76065</t>
         </is>
@@ -1234,17 +1249,17 @@
           <t>DAZEUR Quentin</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>43143</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>36776</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>43141</t>
         </is>
@@ -1327,17 +1342,17 @@
           <t>RYGEL Marek</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>35516</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>35512</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>53303</t>
         </is>
@@ -1420,17 +1435,17 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>35471</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>89134</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -1513,17 +1528,17 @@
           <t>MILNE Laura</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>41678</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>75660</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>75768</t>
         </is>
@@ -1606,17 +1621,17 @@
           <t>ROSA Mathilde</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>75522</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>43572</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>39777</t>
         </is>
@@ -1699,17 +1714,17 @@
           <t>ECKERT Jil-Sophie</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>39762</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>36676</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>39763</t>
         </is>
@@ -1792,17 +1807,17 @@
           <t>VALDENAIRE Mathilde</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>53291</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>56152</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>94782</t>
         </is>
@@ -1885,17 +1900,17 @@
           <t>DIMOVOVA Barbora</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>54343</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>63231</t>
         </is>
@@ -1978,17 +1993,17 @@
           <t>IGNATOV Hristijan</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>35591</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>43799</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>79051</t>
         </is>
@@ -2071,17 +2086,17 @@
           <t>CIOTOLI Francesco</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>63276</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>53269</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>70132</t>
         </is>
@@ -2154,17 +2169,17 @@
           <t>SUDIC Anes</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>41404</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>72217</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>75528</t>
         </is>
@@ -2247,17 +2262,17 @@
           <t>SEDLACEK Alexander</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>36674</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>37309</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>39826</t>
         </is>
@@ -2340,17 +2355,17 @@
           <t>BROWN Frederick</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>36807</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>53202</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>79368</t>
         </is>
@@ -2433,17 +2448,17 @@
           <t>MORANCHO TARDA Arnau</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>37655</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>79289</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>63326</t>
         </is>
@@ -2526,17 +2541,17 @@
           <t>ZAPLETAL Vojtech</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>70681</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>70092</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>43285</t>
         </is>
@@ -2619,17 +2634,17 @@
           <t>BEERSCHWENGER Bjoern</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>36675</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>38995</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>37662</t>
         </is>
@@ -2712,17 +2727,17 @@
           <t>BAROUH Maxence</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>36775</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>56142</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>45024</t>
         </is>
@@ -2805,17 +2820,17 @@
           <t>OVEN Simon</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>37764</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>44341</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>38164</t>
         </is>
@@ -2898,17 +2913,17 @@
           <t>BARTH Lea Sophie</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>66240</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>35175</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>64809</t>
         </is>
@@ -2991,17 +3006,17 @@
           <t>BEZIAT Margot</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>76817</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>76819</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>86154</t>
         </is>
@@ -3084,17 +3099,17 @@
           <t>PALOUDOVA Anezka</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>78808</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>54343</t>
         </is>
@@ -3164,17 +3179,62 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>QUINTARELLI Mattia/MACCAGNAN Davide</t>
+          <t>QUINTARELLI Mattia</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>DELL'AGOSTINO Giorgio/BERNARDI Andrea</t>
+          <t>MACCAGNAN Davide</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>BIANCHETTI Giacomo/CIOTOLI Francesco</t>
+          <t>DELL'AGOSTINO Giorgio</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>BERNARDI Andrea</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>BIANCHETTI Giacomo</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>CIOTOLI Francesco</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>39775</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>53269</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>36551</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>63276</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>75796</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>70132</t>
         </is>
       </c>
     </row>
@@ -3232,17 +3292,62 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>HOCHSCHORNER Pavol/HOCHSCHORNER Peter</t>
+          <t>HOCHSCHORNER Pavol</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>SKANTAR Ladislav/SKANTAR Peter</t>
+          <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>SKAKALA Juraj/GEWISSLER Matus</t>
+          <t>SKANTAR Ladislav</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SKANTAR Peter</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>SKAKALA Juraj</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>GEWISSLER Matus</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>35356</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>35357</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>35360</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>35361</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>39248</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>39249</t>
         </is>
       </c>
     </row>
@@ -3310,17 +3415,62 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>PADILLA Alan/MIRALLES PRATS Xavier</t>
+          <t>PADILLA Alan</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>MORANCHO TARDA Arnau/JIMENEZ German</t>
+          <t>MIRALLES PRATS Xavier</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>RAMOS COLLADO Rodrigo/FREIRE Manuel</t>
+          <t>MORANCHO TARDA Arnau</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>JIMENEZ German</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>RAMOS COLLADO Rodrigo</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>FREIRE Manuel</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>71117</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>37656</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>63326</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>63325</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>37657</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>70071</t>
         </is>
       </c>
     </row>
@@ -3388,17 +3538,62 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>HARTSTEIN Finn/SUELZER Janosch</t>
+          <t>HARTSTEIN Finn</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>WEBER Normen/BRUECKER Rene</t>
+          <t>SUELZER Janosch</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>SCHWARZ Ole/LEMMEN Yannic</t>
+          <t>WEBER Normen</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>BRUECKER Rene</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>SCHWARZ Ole</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>LEMMEN Yannic</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>38995</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>43111</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>36679</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>36680</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>76065</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>45115</t>
         </is>
       </c>
     </row>
@@ -3466,17 +3661,57 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>RYGEL Marek/VESELY Petr</t>
+          <t>RYGEL Marek</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>SUCHANEK Daniel/ROLENC Ondrej</t>
+          <t>VESELY Petr</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>SLANINA Vladimir/SLANINA Vladimir Sen</t>
+          <t>SUCHANEK Daniel</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>ROLENC Ondrej</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SLANINA Vladimir</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SLANINA Vladimir Sen</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>53303</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>35511</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>42246</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>35512</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>43076</t>
         </is>
       </c>
     </row>
@@ -3544,17 +3779,62 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>LAPOINTE Louis/DEBRAY Tony</t>
+          <t>LAPOINTE Louis</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>SANTAMARIA Stephane/DAZEUR Quentin</t>
+          <t>DEBRAY Tony</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>PAZAT Lucas/GOURJAULT Ancelin</t>
+          <t>SANTAMARIA Stephane</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>DAZEUR Quentin</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>PAZAT Lucas</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>GOURJAULT Ancelin</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>43143</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>36776</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>36791</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>43141</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>63164</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>56131</t>
         </is>
       </c>
     </row>
@@ -3726,7 +4006,7 @@
           <t>INZUNZA Maria</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>85122</t>
         </is>
@@ -3789,7 +4069,7 @@
           <t>TORRES BRICENO Marianna</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>75357</t>
         </is>
@@ -3852,7 +4132,7 @@
           <t>MOUHOUB Anais</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>93683</t>
         </is>
@@ -3915,7 +4195,7 @@
           <t>MASSINI Christina</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>87895</t>
         </is>
@@ -3978,7 +4258,7 @@
           <t>HAMANA Toshie</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>42763</t>
         </is>
@@ -4041,7 +4321,7 @@
           <t>BAYEROVA Barbora</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>43180</t>
         </is>
@@ -4104,7 +4384,7 @@
           <t>BROWN Hannah</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>41678</t>
         </is>
@@ -4167,7 +4447,7 @@
           <t>MAENPAA Iisa</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>72267</t>
         </is>
@@ -4230,7 +4510,7 @@
           <t>JAEDICKE Meghan</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>39762</t>
         </is>
@@ -4293,7 +4573,7 @@
           <t>COGGAN Joslin</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>83297</t>
         </is>
@@ -4356,7 +4636,7 @@
           <t>MILNE Laura</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>75768</t>
         </is>
@@ -4419,7 +4699,7 @@
           <t>OXTOBY Lydia</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>61776</t>
         </is>
@@ -4482,7 +4762,7 @@
           <t>VALDENAIRE Mathilde</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>94782</t>
         </is>
@@ -4545,7 +4825,7 @@
           <t>COLLIN Georgina</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>60108</t>
         </is>
@@ -4608,7 +4888,7 @@
           <t>MUELLER Hannah</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>63133</t>
         </is>
@@ -4671,7 +4951,7 @@
           <t>MURRAY Victoria</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>75660</t>
         </is>
@@ -4734,7 +5014,7 @@
           <t>VINET Lise</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>53291</t>
         </is>
@@ -4797,7 +5077,7 @@
           <t>DUPRAS Phenicia</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>56152</t>
         </is>
@@ -4860,7 +5140,7 @@
           <t>DREIER Valentina</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>41612</t>
         </is>
@@ -4923,7 +5203,7 @@
           <t>ECKERT Jil-Sophie</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>39763</t>
         </is>
@@ -4986,7 +5266,7 @@
           <t>PALOUDOVA Anezka</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>54343</t>
         </is>
@@ -5049,7 +5329,7 @@
           <t>FORMENTON Giulia</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>43572</t>
         </is>
@@ -5112,7 +5392,7 @@
           <t>ROSA Mathilde</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>39777</t>
         </is>
@@ -5175,7 +5455,7 @@
           <t>FUESSER Sabine</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>36676</t>
         </is>
@@ -5238,7 +5518,7 @@
           <t>MATHYS Melanie</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>37571</t>
         </is>
@@ -5301,7 +5581,7 @@
           <t>DIMOVOVA Barbora</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>63231</t>
         </is>
@@ -5364,7 +5644,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -5427,7 +5707,7 @@
           <t>TROIANNOS Charalampos</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>72636</t>
         </is>
@@ -5490,7 +5770,7 @@
           <t>PARK Moorim</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>100009</t>
         </is>
@@ -5553,7 +5833,7 @@
           <t>MUTURI Samuel</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>68743</t>
         </is>
@@ -5616,7 +5896,7 @@
           <t>LEUNG Tsz Chun</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>93684</t>
         </is>
@@ -5679,7 +5959,7 @@
           <t>ONG Jun Yi</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>75421</t>
         </is>
@@ -5742,7 +6022,7 @@
           <t>IGNATOV Hristijan</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>79051</t>
         </is>
@@ -5805,7 +6085,7 @@
           <t>MACUS Ondrej</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>94095</t>
         </is>
@@ -5868,7 +6148,7 @@
           <t>KANISCAK Kamil</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>36674</t>
         </is>
@@ -5931,7 +6211,7 @@
           <t>MARTINS MACHADO Joao Vitor</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>103621</t>
         </is>
@@ -5994,7 +6274,7 @@
           <t>BEKKADOUR Mohamed</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>96694</t>
         </is>
@@ -6057,7 +6337,7 @@
           <t>ANDRES Guillermo</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>79289</t>
         </is>
@@ -6120,7 +6400,7 @@
           <t>RAJNIAK Boris</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>37309</t>
         </is>
@@ -6183,7 +6463,7 @@
           <t>MORANCHO TARDA Arnau</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>63326</t>
         </is>
@@ -6246,7 +6526,7 @@
           <t>HAEFELI Robin</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>76130</t>
         </is>
@@ -6309,7 +6589,7 @@
           <t>JEFFERIES Robert</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>53202</t>
         </is>
@@ -6372,7 +6652,7 @@
           <t>SEDLACEK Alexander</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>39826</t>
         </is>
@@ -6435,7 +6715,7 @@
           <t>ZLATAROV Aleksandar</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>43799</t>
         </is>
@@ -6498,7 +6778,7 @@
           <t>MIRALLES PRATS Xavier</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>37656</t>
         </is>
@@ -6561,7 +6841,7 @@
           <t>BROWN Frederick</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>79368</t>
         </is>
@@ -6624,7 +6904,7 @@
           <t>OAKLEY Ben</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>36807</t>
         </is>
@@ -6687,7 +6967,7 @@
           <t>BERNARDI Andrea</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>63276</t>
         </is>
@@ -6750,7 +7030,7 @@
           <t>MACKIC Dusan</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>72217</t>
         </is>
@@ -6813,7 +7093,7 @@
           <t>BOLZERN Linus</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>56069</t>
         </is>
@@ -6876,7 +7156,7 @@
           <t>SPASIKJ Ljubomir</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>35591</t>
         </is>
@@ -6939,7 +7219,7 @@
           <t>DE MIRANDA Lionel</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>95695</t>
         </is>
@@ -7002,7 +7282,7 @@
           <t>BASSETT Kaylen</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>75376</t>
         </is>
@@ -7065,7 +7345,7 @@
           <t>SUDIC Anes</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>75528</t>
         </is>
@@ -7128,7 +7408,7 @@
           <t>CIOTOLI Francesco</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>70132</t>
         </is>
@@ -7191,7 +7471,7 @@
           <t>SAVIC Darko</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>41404</t>
         </is>
@@ -7254,7 +7534,7 @@
           <t>ZAPLETAL Vojtech</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>43285</t>
         </is>
@@ -7317,7 +7597,7 @@
           <t>FIDALGO DE LEON Guillermo</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>37655</t>
         </is>
@@ -7380,7 +7660,7 @@
           <t>NOVAK Tim</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>55802</t>
         </is>
@@ -7443,7 +7723,7 @@
           <t>MORET Hugues</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>56142</t>
         </is>
@@ -7506,7 +7786,7 @@
           <t>MACCAGNAN Davide</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>53269</t>
         </is>
@@ -7569,7 +7849,7 @@
           <t>BARTHEL Bjoern</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>36675</t>
         </is>
@@ -7632,7 +7912,7 @@
           <t>BOUVET Felix</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>36775</t>
         </is>
@@ -7695,7 +7975,7 @@
           <t>HRIC Filip</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>70092</t>
         </is>
@@ -7758,7 +8038,7 @@
           <t>BEERSCHWENGER Bjoern</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>37662</t>
         </is>
@@ -7821,7 +8101,7 @@
           <t>LEMMEN Yannic</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>45115</t>
         </is>
@@ -7884,7 +8164,7 @@
           <t>SLEPICA Karel</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>36509</t>
         </is>
@@ -7947,7 +8227,7 @@
           <t>SATKE Adam</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>70681</t>
         </is>
@@ -8010,7 +8290,7 @@
           <t>HARTSTEIN Finn</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>38995</t>
         </is>
@@ -8073,7 +8353,7 @@
           <t>BAROUH Maxence</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>45024</t>
         </is>
@@ -8136,7 +8416,7 @@
           <t>URANKAR Anze</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>44341</t>
         </is>
@@ -8199,7 +8479,7 @@
           <t>OVEN Simon</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>38164</t>
         </is>
@@ -8262,7 +8542,7 @@
           <t>ZNIDARCIC Nejc</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>37764</t>
         </is>
@@ -8325,7 +8605,7 @@
           <t>FENTANES Ricardo</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>94184</t>
         </is>
@@ -8388,7 +8668,7 @@
           <t>PETRUSHEV Angel</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>94123</t>
         </is>
@@ -8451,7 +8731,7 @@
           <t>NAJIB Mohamad Nazrin</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>75607</t>
         </is>
@@ -8514,7 +8794,7 @@
           <t>KOETSUK Piyanath</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>75406</t>
         </is>
@@ -8577,7 +8857,7 @@
           <t>FONSECA DIAZ Axel</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>82536</t>
         </is>
@@ -8640,7 +8920,7 @@
           <t>FLAGEUL Gokul</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>60016</t>
         </is>
@@ -8703,7 +8983,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -8766,7 +9046,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -8829,7 +9109,7 @@
           <t>SCHOLCZOVA Viktoria</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>89134</t>
         </is>
@@ -8892,7 +9172,7 @@
           <t>BARM Sabrina</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>35175</t>
         </is>
@@ -8955,7 +9235,7 @@
           <t>GAUBERT Elsa</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>76817</t>
         </is>
@@ -9076,7 +9356,7 @@
           <t>BEZIAT Margot</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>86154</t>
         </is>
@@ -9139,7 +9419,7 @@
           <t>GRZIN Alba Zoe</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>39677</t>
         </is>
@@ -9202,7 +9482,7 @@
           <t>KOPUNOVA Katarina</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>35471</t>
         </is>
@@ -9265,7 +9545,7 @@
           <t>PALOUDOVA Anezka</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>54343</t>
         </is>
@@ -9328,7 +9608,7 @@
           <t>RAGUENES Helene</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>76819</t>
         </is>
@@ -9391,7 +9671,7 @@
           <t>RICCIARDI Marlene</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>36550</t>
         </is>
@@ -9454,7 +9734,7 @@
           <t>LUTZ Maren</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>66240</t>
         </is>
@@ -9517,7 +9797,7 @@
           <t>PANATO Cecilia</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>75522</t>
         </is>
@@ -9580,7 +9860,7 @@
           <t>NEMCOVA Marie</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>78808</t>
         </is>
@@ -9643,7 +9923,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -9706,7 +9986,7 @@
           <t>SOSKA Samo</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>89137</t>
         </is>
@@ -9769,7 +10049,7 @@
           <t>SUELZER Janosch</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>43111</t>
         </is>
@@ -9832,7 +10112,7 @@
           <t>COGGAN Peter</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>64679</t>
         </is>
@@ -9895,7 +10175,7 @@
           <t>CHAKIR Issam</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>75631</t>
         </is>
@@ -9958,7 +10238,7 @@
           <t>MEDVED Martin</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>42277</t>
         </is>
@@ -10021,7 +10301,7 @@
           <t>GOJIC Igor</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>36939</t>
         </is>
@@ -10084,7 +10364,7 @@
           <t>TOLIC Ivan</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>39671</t>
         </is>
@@ -10147,7 +10427,7 @@
           <t>BIANCHETTI Giacomo</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>75796</t>
         </is>
@@ -10210,7 +10490,7 @@
           <t>KRISTEK Vaclav</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>39807</t>
         </is>
@@ -10273,7 +10553,7 @@
           <t>FREIRE Manuel</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>70071</t>
         </is>
@@ -10336,7 +10616,7 @@
           <t>RAMOS COLLADO Rodrigo</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>37657</t>
         </is>
@@ -10399,7 +10679,7 @@
           <t>PADILLA Alan</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>71117</t>
         </is>
@@ -10462,7 +10742,7 @@
           <t>MCEWAN Devin</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
@@ -10525,7 +10805,7 @@
           <t>HUNT Ryan</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>53159</t>
         </is>
@@ -10588,7 +10868,7 @@
           <t>DANIK Ladislav</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>82996</t>
         </is>
@@ -10651,7 +10931,7 @@
           <t>OBADIC Luka</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>39639</t>
         </is>
@@ -10714,7 +10994,7 @@
           <t>WEBER Normen</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>36679</t>
         </is>
@@ -10777,7 +11057,7 @@
           <t>SCHWARZ Ole</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>76065</t>
         </is>
@@ -10840,7 +11120,7 @@
           <t>DAZEUR Quentin</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>43141</t>
         </is>
@@ -10903,7 +11183,7 @@
           <t>QUINTARELLI Mattia</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>39775</t>
         </is>
@@ -10966,7 +11246,7 @@
           <t>DEBRAY Tony</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>36776</t>
         </is>
@@ -11029,7 +11309,7 @@
           <t>DELL'AGOSTINO Giorgio</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>36551</t>
         </is>
@@ -11092,7 +11372,7 @@
           <t>LAPOINTE Louis</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>43143</t>
         </is>
@@ -11155,7 +11435,7 @@
           <t>SLANINA Vladimir</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>35516</t>
         </is>
@@ -11218,7 +11498,7 @@
           <t>COF Blaz</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>36897</t>
         </is>
@@ -11281,7 +11561,7 @@
           <t>RYGEL Marek</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>53303</t>
         </is>
@@ -11344,7 +11624,7 @@
           <t>ROLENC Ondrej</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>35512</t>
         </is>
@@ -11407,7 +11687,7 @@
           <t>SARAMANDIF Terence</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>79340</t>
         </is>
@@ -11470,7 +11750,7 @@
           <t>TORRES BRICENO Marianna</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>75357</t>
         </is>
@@ -11533,7 +11813,7 @@
           <t>INZUNZA Maria</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>85122</t>
         </is>
@@ -11596,7 +11876,7 @@
           <t>COGGAN Joslin</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>83297</t>
         </is>
@@ -11659,7 +11939,7 @@
           <t>MOUHOUB Anais</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>93683</t>
         </is>
@@ -11722,7 +12002,7 @@
           <t>MAENPAA Iisa</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>72267</t>
         </is>
@@ -11785,7 +12065,7 @@
           <t>OXTOBY Lydia</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>61776</t>
         </is>
@@ -11848,7 +12128,7 @@
           <t>HAMANA Toshie</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>42763</t>
         </is>
@@ -11911,7 +12191,7 @@
           <t>MURRAY Victoria</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>75660</t>
         </is>
@@ -11974,7 +12254,7 @@
           <t>MILNE Laura</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>75768</t>
         </is>
@@ -12037,7 +12317,7 @@
           <t>JAEDICKE Meghan</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>39762</t>
         </is>
@@ -12100,7 +12380,7 @@
           <t>DREIER Valentina</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>41612</t>
         </is>
@@ -12163,7 +12443,7 @@
           <t>COLLIN Georgina</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>60108</t>
         </is>
@@ -12226,7 +12506,7 @@
           <t>FORMENTON Giulia</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>43572</t>
         </is>
@@ -12289,7 +12569,7 @@
           <t>MUELLER Hannah</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>63133</t>
         </is>
@@ -12352,7 +12632,7 @@
           <t>FUESSER Sabine</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>36676</t>
         </is>
@@ -12415,7 +12695,7 @@
           <t>MASSINI Christina</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>87895</t>
         </is>
@@ -12478,7 +12758,7 @@
           <t>PALOUDOVA Anezka</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>54343</t>
         </is>
@@ -12541,7 +12821,7 @@
           <t>VALDENAIRE Mathilde</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>94782</t>
         </is>
@@ -12604,7 +12884,7 @@
           <t>BROWN Hannah</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>41678</t>
         </is>
@@ -12667,7 +12947,7 @@
           <t>ECKERT Jil-Sophie</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>39763</t>
         </is>
@@ -12730,7 +13010,7 @@
           <t>DUPRAS Phenicia</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>56152</t>
         </is>
@@ -12793,7 +13073,7 @@
           <t>LEUNG Tsz Chun</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>93684</t>
         </is>
@@ -12856,7 +13136,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -12919,7 +13199,7 @@
           <t>PARK Moorim</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>100009</t>
         </is>
@@ -12982,7 +13262,7 @@
           <t>ONG Jun Yi</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>75421</t>
         </is>
@@ -13045,7 +13325,7 @@
           <t>MUTURI Samuel</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>68743</t>
         </is>
@@ -13108,7 +13388,7 @@
           <t>MACUS Ondrej</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>94095</t>
         </is>
@@ -13171,7 +13451,7 @@
           <t>BEKKADOUR Mohamed</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>96694</t>
         </is>
@@ -13234,7 +13514,7 @@
           <t>TROIANNOS Charalampos</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>72636</t>
         </is>
@@ -13297,7 +13577,7 @@
           <t>IGNATOV Hristijan</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>79051</t>
         </is>
@@ -13360,7 +13640,7 @@
           <t>SEDLACEK Alexander</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>39826</t>
         </is>
@@ -13423,7 +13703,7 @@
           <t>RAJNIAK Boris</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>37309</t>
         </is>
@@ -13486,7 +13766,7 @@
           <t>MACKIC Dusan</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>72217</t>
         </is>
@@ -13549,7 +13829,7 @@
           <t>MARTINS MACHADO Joao Vitor</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>103621</t>
         </is>
@@ -13612,7 +13892,7 @@
           <t>MORANCHO TARDA Arnau</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>63326</t>
         </is>
@@ -13675,7 +13955,7 @@
           <t>MIRALLES PRATS Xavier</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>37656</t>
         </is>
@@ -13738,7 +14018,7 @@
           <t>JEFFERIES Robert</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>53202</t>
         </is>
@@ -13801,7 +14081,7 @@
           <t>DE MIRANDA Lionel</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>95695</t>
         </is>
@@ -13864,7 +14144,7 @@
           <t>KANISCAK Kamil</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>36674</t>
         </is>
@@ -13927,7 +14207,7 @@
           <t>SUDIC Anes</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>75528</t>
         </is>
@@ -13990,7 +14270,7 @@
           <t>ANDRES Guillermo</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>79289</t>
         </is>
@@ -14053,7 +14333,7 @@
           <t>BASSETT Kaylen</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>75376</t>
         </is>
@@ -14116,7 +14396,7 @@
           <t>ZLATAROV Aleksandar</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>43799</t>
         </is>
@@ -14179,7 +14459,7 @@
           <t>BROWN Frederick</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>79368</t>
         </is>
@@ -14242,7 +14522,7 @@
           <t>SAVIC Darko</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>41404</t>
         </is>
@@ -14305,7 +14585,7 @@
           <t>SPASIKJ Ljubomir</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>35591</t>
         </is>
@@ -14368,7 +14648,7 @@
           <t>HAEFELI Robin</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>76130</t>
         </is>
@@ -14431,7 +14711,7 @@
           <t>BOLZERN Linus</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>56069</t>
         </is>
@@ -14494,7 +14774,7 @@
           <t>FIDALGO DE LEON Guillermo</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>37655</t>
         </is>
@@ -14557,7 +14837,7 @@
           <t>BARTHEL Bjoern</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>36675</t>
         </is>
@@ -14620,7 +14900,7 @@
           <t>ZAPLETAL Vojtech</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>43285</t>
         </is>
@@ -14683,7 +14963,7 @@
           <t>HARTSTEIN Finn</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>38995</t>
         </is>
@@ -14746,7 +15026,7 @@
           <t>BEERSCHWENGER Bjoern</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>37662</t>
         </is>
@@ -14809,7 +15089,7 @@
           <t>SLEPICA Karel</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>36509</t>
         </is>
@@ -14872,7 +15152,7 @@
           <t>OAKLEY Ben</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>36807</t>
         </is>
@@ -14935,7 +15215,7 @@
           <t>LEMMEN Yannic</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>45115</t>
         </is>
@@ -14998,7 +15278,7 @@
           <t>HRIC Filip</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>70092</t>
         </is>
@@ -15061,7 +15341,7 @@
           <t>BERNARDI Andrea</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>63276</t>
         </is>
@@ -15124,7 +15404,7 @@
           <t>CIOTOLI Francesco</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>70132</t>
         </is>
@@ -15187,7 +15467,7 @@
           <t>MACCAGNAN Davide</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>53269</t>
         </is>
@@ -15250,7 +15530,7 @@
           <t>NOVAK Tim</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>55802</t>
         </is>
@@ -15313,7 +15593,7 @@
           <t>SATKE Adam</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>70681</t>
         </is>
@@ -15376,7 +15656,7 @@
           <t>BOUVET Felix</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>36775</t>
         </is>
@@ -15439,7 +15719,7 @@
           <t>FENTANES Ricardo</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>94184</t>
         </is>
@@ -15502,7 +15782,7 @@
           <t>PETRUSHEV Angel</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>94123</t>
         </is>
@@ -15565,7 +15845,7 @@
           <t>NAJIB Mohamad Nazrin</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>75607</t>
         </is>
@@ -15628,7 +15908,7 @@
           <t>KOETSUK Piyanath</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>75406</t>
         </is>
@@ -15691,7 +15971,7 @@
           <t>FONSECA DIAZ Axel</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>82536</t>
         </is>
@@ -15754,7 +16034,7 @@
           <t>FLAGEUL Gokul</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>60016</t>
         </is>
@@ -15817,7 +16097,7 @@
           <t>GRZIN Alba Zoe</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>39677</t>
         </is>
@@ -15880,7 +16160,7 @@
           <t>SCHOLCZOVA Viktoria</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>89134</t>
         </is>
@@ -16001,7 +16281,7 @@
           <t>BARM Sabrina</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>35175</t>
         </is>
@@ -16064,7 +16344,7 @@
           <t>LUTZ Maren</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>66240</t>
         </is>
@@ -16127,7 +16407,7 @@
           <t>RICCIARDI Marlene</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>36550</t>
         </is>
@@ -16190,7 +16470,7 @@
           <t>KOPUNOVA Katarina</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>35471</t>
         </is>
@@ -16253,7 +16533,7 @@
           <t>BEZIAT Margot</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>86154</t>
         </is>
@@ -16316,7 +16596,7 @@
           <t>PALOUDOVA Anezka</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>54343</t>
         </is>
@@ -16379,7 +16659,7 @@
           <t>RAGUENES Helene</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>76819</t>
         </is>
@@ -16442,7 +16722,7 @@
           <t>CHAKIR Issam</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>75631</t>
         </is>
@@ -16505,7 +16785,7 @@
           <t>COGGAN Peter</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>64679</t>
         </is>
@@ -16568,7 +16848,7 @@
           <t>MEDVED Martin</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>42277</t>
         </is>
@@ -16631,7 +16911,7 @@
           <t>HUNT Ryan</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>53159</t>
         </is>
@@ -16694,7 +16974,7 @@
           <t>MCEWAN Devin</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
@@ -16757,7 +17037,7 @@
           <t>FREIRE Manuel</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>70071</t>
         </is>
@@ -16820,7 +17100,7 @@
           <t>SOSKA Samo</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>89137</t>
         </is>
@@ -16883,7 +17163,7 @@
           <t>RAMOS COLLADO Rodrigo</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>37657</t>
         </is>
@@ -16946,7 +17226,7 @@
           <t>SUELZER Janosch</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>43111</t>
         </is>
@@ -17009,7 +17289,7 @@
           <t>PADILLA Alan</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>71117</t>
         </is>
@@ -17072,7 +17352,7 @@
           <t>GOJIC Igor</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>36939</t>
         </is>
@@ -17135,7 +17415,7 @@
           <t>TOLIC Ivan</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>39671</t>
         </is>
@@ -17198,7 +17478,7 @@
           <t>BIANCHETTI Giacomo</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>75796</t>
         </is>
@@ -17261,7 +17541,7 @@
           <t>DANIK Ladislav</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>82996</t>
         </is>
@@ -17324,7 +17604,7 @@
           <t>OBADIC Luka</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>39639</t>
         </is>
@@ -17387,7 +17667,7 @@
           <t>DELL'AGOSTINO Giorgio</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>36551</t>
         </is>
@@ -17450,7 +17730,7 @@
           <t>KRISTEK Vaclav</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>39807</t>
         </is>
@@ -17513,7 +17793,7 @@
           <t>COF Blaz</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>36897</t>
         </is>
@@ -17576,7 +17856,7 @@
           <t>ROLENC Ondrej</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>35512</t>
         </is>
@@ -17639,7 +17919,7 @@
           <t>SCHWARZ Ole</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>76065</t>
         </is>
@@ -17702,7 +17982,7 @@
           <t>RYGEL Marek</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>53303</t>
         </is>
@@ -17765,7 +18045,7 @@
           <t>QUINTARELLI Mattia</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>39775</t>
         </is>
@@ -17828,7 +18108,7 @@
           <t>SARAMANDIF Terence</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>79340</t>
         </is>
@@ -17891,7 +18171,7 @@
           <t>BAYEROVA Barbora</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>43180</t>
         </is>
@@ -18070,12 +18350,12 @@
           <t>ZAPLETAL Vojtech</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>43186</t>
         </is>
       </c>
-      <c r="V267" t="inlineStr">
+      <c r="Y267" t="inlineStr">
         <is>
           <t>43285</t>
         </is>
@@ -18143,12 +18423,12 @@
           <t>HOLMES Jacob</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>53159</t>
         </is>
       </c>
-      <c r="V268" t="inlineStr">
+      <c r="Y268" t="inlineStr">
         <is>
           <t>53139</t>
         </is>
@@ -18216,12 +18496,12 @@
           <t>JIMENEZ German</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>63326</t>
         </is>
       </c>
-      <c r="V269" t="inlineStr">
+      <c r="Y269" t="inlineStr">
         <is>
           <t>63325</t>
         </is>
@@ -18289,12 +18569,12 @@
           <t>GEWISSLER Matus</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
       </c>
-      <c r="V270" t="inlineStr">
+      <c r="Y270" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
@@ -18362,12 +18642,12 @@
           <t>BASSETT Lachlan</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>75376</t>
         </is>
       </c>
-      <c r="V271" t="inlineStr">
+      <c r="Y271" t="inlineStr">
         <is>
           <t>59988</t>
         </is>
@@ -18435,12 +18715,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V272" t="inlineStr">
+      <c r="Y272" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -18508,12 +18788,12 @@
           <t>TOLIC Ivan</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>39639</t>
         </is>
       </c>
-      <c r="V273" t="inlineStr">
+      <c r="Y273" t="inlineStr">
         <is>
           <t>39671</t>
         </is>
@@ -18581,12 +18861,12 @@
           <t>SLANINA Vladimir Sen</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>35516</t>
         </is>
       </c>
-      <c r="V274" t="inlineStr">
+      <c r="Y274" t="inlineStr">
         <is>
           <t>43076</t>
         </is>
@@ -18654,12 +18934,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V275" t="inlineStr">
+      <c r="Y275" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -18727,12 +19007,12 @@
           <t>SUELZER Janosch</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>76065</t>
         </is>
       </c>
-      <c r="V276" t="inlineStr">
+      <c r="Y276" t="inlineStr">
         <is>
           <t>43111</t>
         </is>
@@ -18800,12 +19080,12 @@
           <t>ROLENC Ondrej</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>42246</t>
         </is>
       </c>
-      <c r="V277" t="inlineStr">
+      <c r="Y277" t="inlineStr">
         <is>
           <t>35512</t>
         </is>
@@ -18873,12 +19153,12 @@
           <t>MIRALLES PRATS Xavier</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>71117</t>
         </is>
       </c>
-      <c r="V278" t="inlineStr">
+      <c r="Y278" t="inlineStr">
         <is>
           <t>37656</t>
         </is>
@@ -18946,12 +19226,12 @@
           <t>GOURJAULT Ancelin</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>63164</t>
         </is>
       </c>
-      <c r="V279" t="inlineStr">
+      <c r="Y279" t="inlineStr">
         <is>
           <t>56131</t>
         </is>
@@ -19019,12 +19299,12 @@
           <t>FREIRE Manuel</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>37657</t>
         </is>
       </c>
-      <c r="V280" t="inlineStr">
+      <c r="Y280" t="inlineStr">
         <is>
           <t>70071</t>
         </is>
@@ -19092,12 +19372,12 @@
           <t>DELL'AGOSTINO Giorgio</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>39775</t>
         </is>
       </c>
-      <c r="V281" t="inlineStr">
+      <c r="Y281" t="inlineStr">
         <is>
           <t>36551</t>
         </is>
@@ -19165,12 +19445,12 @@
           <t>VESELY Petr</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>53303</t>
         </is>
       </c>
-      <c r="V282" t="inlineStr">
+      <c r="Y282" t="inlineStr">
         <is>
           <t>35511</t>
         </is>
@@ -19238,12 +19518,12 @@
           <t>DEBRAY Tony</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>43143</t>
         </is>
       </c>
-      <c r="V283" t="inlineStr">
+      <c r="Y283" t="inlineStr">
         <is>
           <t>36776</t>
         </is>
@@ -19311,12 +19591,12 @@
           <t>DAZEUR Quentin</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>36791</t>
         </is>
       </c>
-      <c r="V284" t="inlineStr">
+      <c r="Y284" t="inlineStr">
         <is>
           <t>43141</t>
         </is>
@@ -19384,12 +19664,12 @@
           <t>BEZIAT Margot</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>76817</t>
         </is>
       </c>
-      <c r="V285" t="inlineStr">
+      <c r="Y285" t="inlineStr">
         <is>
           <t>86154</t>
         </is>
@@ -19457,12 +19737,12 @@
           <t>FEINE Constanze</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>64809</t>
         </is>
       </c>
-      <c r="V286" t="inlineStr">
+      <c r="Y286" t="inlineStr">
         <is>
           <t>93970</t>
         </is>
@@ -19530,12 +19810,12 @@
           <t>SCHOLCZOVA Viktoria</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>35471</t>
         </is>
       </c>
-      <c r="V287" t="inlineStr">
+      <c r="Y287" t="inlineStr">
         <is>
           <t>89134</t>
         </is>
@@ -19603,12 +19883,12 @@
           <t>BARM Sabrina</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>66240</t>
         </is>
       </c>
-      <c r="V288" t="inlineStr">
+      <c r="Y288" t="inlineStr">
         <is>
           <t>35175</t>
         </is>
@@ -19676,12 +19956,12 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>78808</t>
         </is>
       </c>
-      <c r="V289" t="inlineStr">
+      <c r="Y289" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -19749,12 +20029,12 @@
           <t>PANATO Cecilia</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>36550</t>
         </is>
       </c>
-      <c r="V290" t="inlineStr">
+      <c r="Y290" t="inlineStr">
         <is>
           <t>75522</t>
         </is>
@@ -19822,7 +20102,7 @@
           <t>COLLIN Georgina</t>
         </is>
       </c>
-      <c r="V291" t="inlineStr">
+      <c r="Y291" t="inlineStr">
         <is>
           <t>60108</t>
         </is>
@@ -19890,12 +20170,12 @@
           <t>JIMENEZ German</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>63326</t>
         </is>
       </c>
-      <c r="V292" t="inlineStr">
+      <c r="Y292" t="inlineStr">
         <is>
           <t>63325</t>
         </is>
@@ -19963,12 +20243,12 @@
           <t>SLANINA Vladimir Sen</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>35516</t>
         </is>
       </c>
-      <c r="V293" t="inlineStr">
+      <c r="Y293" t="inlineStr">
         <is>
           <t>43076</t>
         </is>
@@ -20036,12 +20316,12 @@
           <t>HOLMES Jacob</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>53159</t>
         </is>
       </c>
-      <c r="V294" t="inlineStr">
+      <c r="Y294" t="inlineStr">
         <is>
           <t>53139</t>
         </is>
@@ -20109,12 +20389,12 @@
           <t>MIRALLES PRATS Xavier</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>71117</t>
         </is>
       </c>
-      <c r="V295" t="inlineStr">
+      <c r="Y295" t="inlineStr">
         <is>
           <t>37656</t>
         </is>
@@ -20182,12 +20462,12 @@
           <t>FREIRE Manuel</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>37657</t>
         </is>
       </c>
-      <c r="V296" t="inlineStr">
+      <c r="Y296" t="inlineStr">
         <is>
           <t>70071</t>
         </is>
@@ -20255,12 +20535,12 @@
           <t>BASSETT Lachlan</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>75376</t>
         </is>
       </c>
-      <c r="V297" t="inlineStr">
+      <c r="Y297" t="inlineStr">
         <is>
           <t>59988</t>
         </is>
@@ -20328,12 +20608,12 @@
           <t>SUELZER Janosch</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>76065</t>
         </is>
       </c>
-      <c r="V298" t="inlineStr">
+      <c r="Y298" t="inlineStr">
         <is>
           <t>43111</t>
         </is>
@@ -20401,12 +20681,12 @@
           <t>ZAPLETAL Vojtech</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>43186</t>
         </is>
       </c>
-      <c r="V299" t="inlineStr">
+      <c r="Y299" t="inlineStr">
         <is>
           <t>43285</t>
         </is>
@@ -20474,12 +20754,12 @@
           <t>TOLIC Ivan</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>39639</t>
         </is>
       </c>
-      <c r="V300" t="inlineStr">
+      <c r="Y300" t="inlineStr">
         <is>
           <t>39671</t>
         </is>
@@ -20547,12 +20827,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V301" t="inlineStr">
+      <c r="Y301" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -20620,12 +20900,12 @@
           <t>DELL'AGOSTINO Giorgio</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>39775</t>
         </is>
       </c>
-      <c r="V302" t="inlineStr">
+      <c r="Y302" t="inlineStr">
         <is>
           <t>36551</t>
         </is>
@@ -20693,12 +20973,12 @@
           <t>GEWISSLER Matus</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
       </c>
-      <c r="V303" t="inlineStr">
+      <c r="Y303" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
@@ -20766,12 +21046,12 @@
           <t>GOURJAULT Ancelin</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>63164</t>
         </is>
       </c>
-      <c r="V304" t="inlineStr">
+      <c r="Y304" t="inlineStr">
         <is>
           <t>56131</t>
         </is>
@@ -20790,7 +21070,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -20800,7 +21080,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Heats</t>
+          <t>Forerunner</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -20815,47 +21095,27 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>15:46:30</t>
+          <t>16:50:03</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="J305" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K305" t="n">
         <v>304</v>
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>WEBER Normen</t>
-        </is>
-      </c>
-      <c r="S305" t="inlineStr">
-        <is>
-          <t>BRUECKER Rene</t>
-        </is>
-      </c>
-      <c r="U305" t="inlineStr">
-        <is>
-          <t>36679</t>
-        </is>
-      </c>
-      <c r="V305" t="inlineStr">
-        <is>
-          <t>36680</t>
+          <t>GILART Eric</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>SENIOR</t>
@@ -20888,7 +21148,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>16:50:03</t>
+          <t>16:51:01</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -20897,18 +21157,23 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K306" t="n">
         <v>305</v>
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>GILART Eric</t>
+          <t>TEIXIDO Jordi</t>
         </is>
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>SENIOR</t>
@@ -20926,7 +21191,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Forerunner</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -20941,12 +21206,12 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>16:51:01</t>
+          <t>17:03:02</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J307" t="n">
@@ -20955,16 +21220,31 @@
       <c r="K307" t="n">
         <v>306</v>
       </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>TEIXIDO Jordi</t>
+          <t>MURRAY Victoria</t>
+        </is>
+      </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>75660</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20984,7 +21264,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Heats</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -20999,28 +21279,38 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>16:53:30</t>
+          <t>17:04:32</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>LAT</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="J308" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="K308" t="n">
         <v>307</v>
       </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>STANOVSKY Samuel</t>
-        </is>
-      </c>
-      <c r="U308" t="inlineStr">
-        <is>
-          <t>84121</t>
+          <t>DREIER Valentina</t>
+        </is>
+      </c>
+      <c r="X308" t="inlineStr">
+        <is>
+          <t>41612</t>
         </is>
       </c>
     </row>
@@ -21062,38 +21352,38 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>17:03:02</t>
+          <t>17:06:02</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>SUI</t>
         </is>
       </c>
       <c r="J309" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K309" t="n">
         <v>308</v>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>MURRAY Victoria</t>
-        </is>
-      </c>
-      <c r="U309" t="inlineStr">
-        <is>
-          <t>75660</t>
+          <t>MUELLER Hannah</t>
+        </is>
+      </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>63133</t>
         </is>
       </c>
     </row>
@@ -21135,38 +21425,38 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>17:04:32</t>
+          <t>17:07:33</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J310" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K310" t="n">
         <v>309</v>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>DREIER Valentina</t>
-        </is>
-      </c>
-      <c r="U310" t="inlineStr">
-        <is>
-          <t>41612</t>
+          <t>FUESSER Sabine</t>
+        </is>
+      </c>
+      <c r="X310" t="inlineStr">
+        <is>
+          <t>36676</t>
         </is>
       </c>
     </row>
@@ -21208,38 +21498,38 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>17:06:02</t>
+          <t>17:09:02</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>SUI</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J311" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K311" t="n">
         <v>310</v>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>MUELLER Hannah</t>
-        </is>
-      </c>
-      <c r="U311" t="inlineStr">
-        <is>
-          <t>63133</t>
+          <t>VALDENAIRE Mathilde</t>
+        </is>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>94782</t>
         </is>
       </c>
     </row>
@@ -21281,7 +21571,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>17:07:33</t>
+          <t>17:10:35</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -21290,29 +21580,29 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K312" t="n">
         <v>311</v>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>FUESSER Sabine</t>
-        </is>
-      </c>
-      <c r="U312" t="inlineStr">
-        <is>
-          <t>36676</t>
+          <t>ECKERT Jil-Sophie</t>
+        </is>
+      </c>
+      <c r="X312" t="inlineStr">
+        <is>
+          <t>39763</t>
         </is>
       </c>
     </row>
@@ -21354,38 +21644,38 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>17:09:02</t>
+          <t>17:12:05</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J313" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K313" t="n">
         <v>312</v>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>VALDENAIRE Mathilde</t>
-        </is>
-      </c>
-      <c r="U313" t="inlineStr">
-        <is>
-          <t>94782</t>
+          <t>BROWN Hannah</t>
+        </is>
+      </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>41678</t>
         </is>
       </c>
     </row>
@@ -21427,38 +21717,38 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>17:10:35</t>
+          <t>17:13:31</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J314" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K314" t="n">
         <v>313</v>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>ECKERT Jil-Sophie</t>
-        </is>
-      </c>
-      <c r="U314" t="inlineStr">
-        <is>
-          <t>39763</t>
+          <t>DUPRAS Phenicia</t>
+        </is>
+      </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>56152</t>
         </is>
       </c>
     </row>
@@ -21500,38 +21790,38 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>17:12:05</t>
+          <t>17:15:02</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J315" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K315" t="n">
         <v>314</v>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>BROWN Hannah</t>
-        </is>
-      </c>
-      <c r="U315" t="inlineStr">
-        <is>
-          <t>41678</t>
+          <t>MASSINI Christina</t>
+        </is>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>87895</t>
         </is>
       </c>
     </row>
@@ -21573,38 +21863,38 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>17:13:31</t>
+          <t>17:16:33</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J316" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K316" t="n">
         <v>315</v>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>DUPRAS Phenicia</t>
-        </is>
-      </c>
-      <c r="U316" t="inlineStr">
-        <is>
-          <t>56152</t>
+          <t>PALOUDOVA Anezka</t>
+        </is>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>54343</t>
         </is>
       </c>
     </row>
@@ -21646,38 +21936,38 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>17:15:02</t>
+          <t>17:18:04</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J317" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K317" t="n">
         <v>316</v>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>MASSINI Christina</t>
-        </is>
-      </c>
-      <c r="U317" t="inlineStr">
-        <is>
-          <t>87895</t>
+          <t>VINET Lise</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>53291</t>
         </is>
       </c>
     </row>
@@ -21719,38 +22009,38 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>17:16:33</t>
+          <t>17:19:33</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SUI</t>
         </is>
       </c>
       <c r="J318" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K318" t="n">
         <v>317</v>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>PALOUDOVA Anezka</t>
-        </is>
-      </c>
-      <c r="U318" t="inlineStr">
-        <is>
-          <t>54343</t>
+          <t>MATHYS Melanie</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>37571</t>
         </is>
       </c>
     </row>
@@ -21792,38 +22082,38 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>17:18:04</t>
+          <t>17:21:04</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J319" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K319" t="n">
         <v>318</v>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>VINET Lise</t>
-        </is>
-      </c>
-      <c r="U319" t="inlineStr">
-        <is>
-          <t>53291</t>
+          <t>DIMOVOVA Barbora</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>63231</t>
         </is>
       </c>
     </row>
@@ -21865,38 +22155,38 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>17:19:33</t>
+          <t>17:22:31</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>SUI</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J320" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K320" t="n">
         <v>319</v>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>MATHYS Melanie</t>
-        </is>
-      </c>
-      <c r="U320" t="inlineStr">
-        <is>
-          <t>37571</t>
+          <t>SATKOVA Martina</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>42008</t>
         </is>
       </c>
     </row>
@@ -21913,7 +22203,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -21923,7 +22213,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Heats</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -21938,35 +22228,45 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>17:20:30</t>
+          <t>17:23:57</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J321" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K321" t="n">
         <v>320</v>
       </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>STANOVSKA Sona</t>
-        </is>
-      </c>
-      <c r="U321" t="inlineStr">
-        <is>
-          <t>51647</t>
+          <t>ROSA Mathilde</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>39777</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21976,7 +22276,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -22001,45 +22301,45 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>17:21:04</t>
+          <t>17:29:32</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>CRO</t>
         </is>
       </c>
       <c r="J322" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K322" t="n">
         <v>321</v>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>DIMOVOVA Barbora</t>
-        </is>
-      </c>
-      <c r="U322" t="inlineStr">
-        <is>
-          <t>63231</t>
+          <t>OBADIC Luka</t>
+        </is>
+      </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>39639</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -22049,7 +22349,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -22074,45 +22374,45 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>17:22:31</t>
+          <t>17:31:01</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J323" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K323" t="n">
         <v>322</v>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>SATKOVA Martina</t>
-        </is>
-      </c>
-      <c r="U323" t="inlineStr">
-        <is>
-          <t>42008</t>
+          <t>QUINTARELLI Mattia</t>
+        </is>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>39775</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -22122,7 +22422,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -22147,38 +22447,38 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>17:23:57</t>
+          <t>17:32:36</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J324" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="K324" t="n">
         <v>323</v>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>ROSA Mathilde</t>
-        </is>
-      </c>
-      <c r="U324" t="inlineStr">
-        <is>
-          <t>39777</t>
+          <t>KRISTEK Vaclav</t>
+        </is>
+      </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>39807</t>
         </is>
       </c>
     </row>
@@ -22220,38 +22520,38 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>17:29:32</t>
+          <t>17:34:03</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>CRO</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J325" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K325" t="n">
         <v>324</v>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>OBADIC Luka</t>
-        </is>
-      </c>
-      <c r="U325" t="inlineStr">
-        <is>
-          <t>39639</t>
+          <t>SCHWARZ Ole</t>
+        </is>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>76065</t>
         </is>
       </c>
     </row>
@@ -22293,38 +22593,38 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>17:31:01</t>
+          <t>17:35:36</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J326" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K326" t="n">
         <v>325</v>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>QUINTARELLI Mattia</t>
-        </is>
-      </c>
-      <c r="U326" t="inlineStr">
-        <is>
-          <t>39775</t>
+          <t>RYGEL Marek</t>
+        </is>
+      </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>53303</t>
         </is>
       </c>
     </row>
@@ -22366,38 +22666,38 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>17:32:36</t>
+          <t>17:37:02</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J327" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="K327" t="n">
         <v>326</v>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>KRISTEK Vaclav</t>
-        </is>
-      </c>
-      <c r="U327" t="inlineStr">
-        <is>
-          <t>39807</t>
+          <t>COF Blaz</t>
+        </is>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>36897</t>
         </is>
       </c>
     </row>
@@ -22439,38 +22739,38 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>17:34:03</t>
+          <t>17:38:32</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J328" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K328" t="n">
         <v>327</v>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>SCHWARZ Ole</t>
-        </is>
-      </c>
-      <c r="U328" t="inlineStr">
-        <is>
-          <t>76065</t>
+          <t>ROLENC Ondrej</t>
+        </is>
+      </c>
+      <c r="X328" t="inlineStr">
+        <is>
+          <t>35512</t>
         </is>
       </c>
     </row>
@@ -22512,38 +22812,38 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>17:35:36</t>
+          <t>17:40:04</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J329" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K329" t="n">
         <v>328</v>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>RYGEL Marek</t>
-        </is>
-      </c>
-      <c r="U329" t="inlineStr">
-        <is>
-          <t>53303</t>
+          <t>DEBRAY Tony</t>
+        </is>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>36776</t>
         </is>
       </c>
     </row>
@@ -22585,38 +22885,38 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>17:37:02</t>
+          <t>17:41:33</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J330" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K330" t="n">
         <v>329</v>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>COF Blaz</t>
-        </is>
-      </c>
-      <c r="U330" t="inlineStr">
-        <is>
-          <t>36897</t>
+          <t>DAZEUR Quentin</t>
+        </is>
+      </c>
+      <c r="X330" t="inlineStr">
+        <is>
+          <t>43141</t>
         </is>
       </c>
     </row>
@@ -22658,38 +22958,38 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>17:38:32</t>
+          <t>17:43:07</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J331" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K331" t="n">
         <v>330</v>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>ROLENC Ondrej</t>
-        </is>
-      </c>
-      <c r="U331" t="inlineStr">
-        <is>
-          <t>35512</t>
+          <t>WEBER Normen</t>
+        </is>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>36679</t>
         </is>
       </c>
     </row>
@@ -22731,38 +23031,38 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>17:40:04</t>
+          <t>17:44:34</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J332" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K332" t="n">
         <v>331</v>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>DEBRAY Tony</t>
-        </is>
-      </c>
-      <c r="U332" t="inlineStr">
-        <is>
-          <t>36776</t>
+          <t>SLANINA Vladimir</t>
+        </is>
+      </c>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>35516</t>
         </is>
       </c>
     </row>
@@ -22804,7 +23104,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>17:41:33</t>
+          <t>17:46:01</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -22813,29 +23113,29 @@
         </is>
       </c>
       <c r="J333" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K333" t="n">
         <v>332</v>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>DAZEUR Quentin</t>
-        </is>
-      </c>
-      <c r="U333" t="inlineStr">
-        <is>
-          <t>43141</t>
+          <t>LAPOINTE Louis</t>
+        </is>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>43143</t>
         </is>
       </c>
     </row>
@@ -22852,7 +23152,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -22877,7 +23177,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>17:43:07</t>
+          <t>17:51:35</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -22886,29 +23186,29 @@
         </is>
       </c>
       <c r="J334" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K334" t="n">
         <v>333</v>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>WEBER Normen</t>
-        </is>
-      </c>
-      <c r="U334" t="inlineStr">
-        <is>
-          <t>36679</t>
+          <t>LEMMEN Yannic</t>
+        </is>
+      </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>45115</t>
         </is>
       </c>
     </row>
@@ -22925,7 +23225,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -22950,7 +23250,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>17:44:34</t>
+          <t>17:53:04</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -22959,29 +23259,29 @@
         </is>
       </c>
       <c r="J335" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K335" t="n">
         <v>334</v>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>SLANINA Vladimir</t>
-        </is>
-      </c>
-      <c r="U335" t="inlineStr">
-        <is>
-          <t>35516</t>
+          <t>SATKE Adam</t>
+        </is>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>70681</t>
         </is>
       </c>
     </row>
@@ -22998,7 +23298,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -23023,12 +23323,12 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>17:46:01</t>
+          <t>17:54:33</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J336" t="n">
@@ -23039,22 +23339,22 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>LAPOINTE Louis</t>
-        </is>
-      </c>
-      <c r="U336" t="inlineStr">
-        <is>
-          <t>43143</t>
+          <t>HARTSTEIN Finn</t>
+        </is>
+      </c>
+      <c r="X336" t="inlineStr">
+        <is>
+          <t>38995</t>
         </is>
       </c>
     </row>
@@ -23096,38 +23396,38 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>17:51:35</t>
+          <t>17:56:05</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>SUI</t>
         </is>
       </c>
       <c r="J337" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="K337" t="n">
         <v>336</v>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>LEMMEN Yannic</t>
-        </is>
-      </c>
-      <c r="U337" t="inlineStr">
-        <is>
-          <t>45115</t>
+          <t>BOLZERN Linus</t>
+        </is>
+      </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>56069</t>
         </is>
       </c>
     </row>
@@ -23169,7 +23469,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>17:53:04</t>
+          <t>17:57:36</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -23178,29 +23478,29 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K338" t="n">
         <v>337</v>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
         <is>
-          <t>SATKE Adam</t>
-        </is>
-      </c>
-      <c r="U338" t="inlineStr">
-        <is>
-          <t>70681</t>
+          <t>HRIC Filip</t>
+        </is>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>70092</t>
         </is>
       </c>
     </row>
@@ -23242,38 +23542,38 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>17:54:33</t>
+          <t>17:59:03</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J339" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="K339" t="n">
         <v>338</v>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>HARTSTEIN Finn</t>
-        </is>
-      </c>
-      <c r="U339" t="inlineStr">
-        <is>
-          <t>38995</t>
+          <t>OAKLEY Ben</t>
+        </is>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>36807</t>
         </is>
       </c>
     </row>
@@ -23315,38 +23615,38 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>17:56:05</t>
+          <t>18:00:34</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>SUI</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J340" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K340" t="n">
         <v>339</v>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>BOLZERN Linus</t>
-        </is>
-      </c>
-      <c r="U340" t="inlineStr">
-        <is>
-          <t>56069</t>
+          <t>ZAPLETAL Vojtech</t>
+        </is>
+      </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>43285</t>
         </is>
       </c>
     </row>
@@ -23388,38 +23688,38 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>17:57:36</t>
+          <t>18:02:03</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J341" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K341" t="n">
         <v>340</v>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
         <is>
-          <t>HRIC Filip</t>
-        </is>
-      </c>
-      <c r="U341" t="inlineStr">
-        <is>
-          <t>70092</t>
+          <t>BEERSCHWENGER Bjoern</t>
+        </is>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>37662</t>
         </is>
       </c>
     </row>
@@ -23461,38 +23761,38 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>17:59:03</t>
+          <t>18:03:32</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J342" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K342" t="n">
         <v>341</v>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>OAKLEY Ben</t>
-        </is>
-      </c>
-      <c r="U342" t="inlineStr">
-        <is>
-          <t>36807</t>
+          <t>NOVAK Tim</t>
+        </is>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>55802</t>
         </is>
       </c>
     </row>
@@ -23534,38 +23834,38 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>18:00:34</t>
+          <t>18:05:00</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J343" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K343" t="n">
         <v>342</v>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
         <is>
-          <t>ZAPLETAL Vojtech</t>
-        </is>
-      </c>
-      <c r="U343" t="inlineStr">
-        <is>
-          <t>43285</t>
+          <t>BOUVET Felix</t>
+        </is>
+      </c>
+      <c r="X343" t="inlineStr">
+        <is>
+          <t>36775</t>
         </is>
       </c>
     </row>
@@ -23607,38 +23907,38 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>18:02:03</t>
+          <t>18:06:34</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J344" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K344" t="n">
         <v>343</v>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
         <is>
-          <t>BEERSCHWENGER Bjoern</t>
-        </is>
-      </c>
-      <c r="U344" t="inlineStr">
-        <is>
-          <t>37662</t>
+          <t>OVEN Simon</t>
+        </is>
+      </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>38164</t>
         </is>
       </c>
     </row>
@@ -23680,38 +23980,38 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>18:03:32</t>
+          <t>18:08:01</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J345" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K345" t="n">
         <v>344</v>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
         <is>
-          <t>NOVAK Tim</t>
-        </is>
-      </c>
-      <c r="U345" t="inlineStr">
-        <is>
-          <t>55802</t>
+          <t>BAROUH Maxence</t>
+        </is>
+      </c>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>45024</t>
         </is>
       </c>
     </row>
@@ -23753,7 +24053,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>18:05:00</t>
+          <t>18:09:32</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -23762,29 +24062,29 @@
         </is>
       </c>
       <c r="J346" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K346" t="n">
         <v>345</v>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
         <is>
-          <t>BOUVET Felix</t>
-        </is>
-      </c>
-      <c r="U346" t="inlineStr">
-        <is>
-          <t>36775</t>
+          <t>MORET Hugues</t>
+        </is>
+      </c>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>56142</t>
         </is>
       </c>
     </row>
@@ -23826,7 +24126,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>18:06:34</t>
+          <t>18:11:02</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -23835,29 +24135,29 @@
         </is>
       </c>
       <c r="J347" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K347" t="n">
         <v>346</v>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
         <is>
-          <t>OVEN Simon</t>
-        </is>
-      </c>
-      <c r="U347" t="inlineStr">
-        <is>
-          <t>38164</t>
+          <t>ZNIDARCIC Nejc</t>
+        </is>
+      </c>
+      <c r="X347" t="inlineStr">
+        <is>
+          <t>37764</t>
         </is>
       </c>
     </row>
@@ -23899,45 +24199,45 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>18:08:01</t>
+          <t>18:12:33</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J348" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K348" t="n">
         <v>347</v>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
         <is>
-          <t>BAROUH Maxence</t>
-        </is>
-      </c>
-      <c r="U348" t="inlineStr">
-        <is>
-          <t>45024</t>
+          <t>URANKAR Anze</t>
+        </is>
+      </c>
+      <c r="X348" t="inlineStr">
+        <is>
+          <t>44341</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -23947,7 +24247,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -23972,45 +24272,45 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>18:09:32</t>
+          <t>18:18:00</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J349" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K349" t="n">
         <v>348</v>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
         <is>
-          <t>MORET Hugues</t>
-        </is>
-      </c>
-      <c r="U349" t="inlineStr">
-        <is>
-          <t>56142</t>
+          <t>LUTZ Maren</t>
+        </is>
+      </c>
+      <c r="X349" t="inlineStr">
+        <is>
+          <t>66240</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -24020,7 +24320,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -24045,45 +24345,45 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>18:11:02</t>
+          <t>18:19:29</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J350" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K350" t="n">
         <v>349</v>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
         <is>
-          <t>ZNIDARCIC Nejc</t>
-        </is>
-      </c>
-      <c r="U350" t="inlineStr">
-        <is>
-          <t>37764</t>
+          <t>RICCIARDI Marlene</t>
+        </is>
+      </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>36550</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -24093,7 +24393,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -24118,38 +24418,38 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>18:12:33</t>
+          <t>18:21:05</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J351" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K351" t="n">
         <v>350</v>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
         <is>
-          <t>URANKAR Anze</t>
-        </is>
-      </c>
-      <c r="U351" t="inlineStr">
-        <is>
-          <t>44341</t>
+          <t>RAGUENES Helene</t>
+        </is>
+      </c>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>76819</t>
         </is>
       </c>
     </row>
@@ -24191,38 +24491,38 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>18:18:00</t>
+          <t>18:22:34</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>CRO</t>
         </is>
       </c>
       <c r="J352" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K352" t="n">
         <v>351</v>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
         <is>
-          <t>LUTZ Maren</t>
-        </is>
-      </c>
-      <c r="U352" t="inlineStr">
-        <is>
-          <t>66240</t>
+          <t>GRZIN Alba Zoe</t>
+        </is>
+      </c>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>39677</t>
         </is>
       </c>
     </row>
@@ -24264,38 +24564,38 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>18:19:29</t>
+          <t>18:24:05</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J353" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K353" t="n">
         <v>352</v>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
         <is>
-          <t>RICCIARDI Marlene</t>
-        </is>
-      </c>
-      <c r="U353" t="inlineStr">
-        <is>
-          <t>36550</t>
+          <t>BEZIAT Margot</t>
+        </is>
+      </c>
+      <c r="X353" t="inlineStr">
+        <is>
+          <t>86154</t>
         </is>
       </c>
     </row>
@@ -24337,38 +24637,38 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>18:21:05</t>
+          <t>18:25:33</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J354" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K354" t="n">
         <v>353</v>
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
         <is>
-          <t>RAGUENES Helene</t>
-        </is>
-      </c>
-      <c r="U354" t="inlineStr">
-        <is>
-          <t>76819</t>
+          <t>PALOUDOVA Anezka</t>
+        </is>
+      </c>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>54343</t>
         </is>
       </c>
     </row>
@@ -24410,38 +24710,38 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>18:22:34</t>
+          <t>18:27:05</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>CRO</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J355" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K355" t="n">
         <v>354</v>
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
         <is>
-          <t>GRZIN Alba Zoe</t>
-        </is>
-      </c>
-      <c r="U355" t="inlineStr">
-        <is>
-          <t>39677</t>
+          <t>KOPUNOVA Katarina</t>
+        </is>
+      </c>
+      <c r="X355" t="inlineStr">
+        <is>
+          <t>35471</t>
         </is>
       </c>
     </row>
@@ -24483,38 +24783,38 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>18:24:05</t>
+          <t>18:28:31</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J356" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K356" t="n">
         <v>355</v>
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
         <is>
-          <t>BEZIAT Margot</t>
-        </is>
-      </c>
-      <c r="U356" t="inlineStr">
-        <is>
-          <t>86154</t>
+          <t>KNEBLOVA Tereza</t>
+        </is>
+      </c>
+      <c r="X356" t="inlineStr">
+        <is>
+          <t>83782</t>
         </is>
       </c>
     </row>
@@ -24556,38 +24856,38 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>18:25:33</t>
+          <t>18:30:05</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J357" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K357" t="n">
         <v>356</v>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
         <is>
-          <t>PALOUDOVA Anezka</t>
-        </is>
-      </c>
-      <c r="U357" t="inlineStr">
-        <is>
-          <t>54343</t>
+          <t>GAUBERT Elsa</t>
+        </is>
+      </c>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>76817</t>
         </is>
       </c>
     </row>
@@ -24629,38 +24929,38 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>18:27:05</t>
+          <t>18:31:31</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J358" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K358" t="n">
         <v>357</v>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t>KOPUNOVA Katarina</t>
-        </is>
-      </c>
-      <c r="U358" t="inlineStr">
-        <is>
-          <t>35471</t>
+          <t>SATKOVA Martina</t>
+        </is>
+      </c>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>42008</t>
         </is>
       </c>
     </row>
@@ -24702,38 +25002,38 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>18:28:31</t>
+          <t>18:33:01</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J359" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="K359" t="n">
         <v>358</v>
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
         <is>
-          <t>KNEBLOVA Tereza</t>
-        </is>
-      </c>
-      <c r="U359" t="inlineStr">
-        <is>
-          <t>83782</t>
+          <t>PANATO Cecilia</t>
+        </is>
+      </c>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>75522</t>
         </is>
       </c>
     </row>
@@ -24775,45 +25075,45 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>18:30:05</t>
+          <t>18:34:34</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J360" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K360" t="n">
         <v>359</v>
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
         <is>
-          <t>GAUBERT Elsa</t>
-        </is>
-      </c>
-      <c r="U360" t="inlineStr">
-        <is>
-          <t>76817</t>
+          <t>NEMCOVA Marie</t>
+        </is>
+      </c>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>78808</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -24823,7 +25123,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -24848,45 +25148,55 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>18:31:31</t>
+          <t>18:40:01</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="J361" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K361" t="n">
         <v>360</v>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
         <is>
-          <t>SATKOVA Martina</t>
-        </is>
-      </c>
-      <c r="U361" t="inlineStr">
-        <is>
-          <t>42008</t>
+          <t>BASSETT Kaylen</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>BASSETT Lachlan</t>
+        </is>
+      </c>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>75376</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>59988</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -24896,7 +25206,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -24921,45 +25231,55 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>18:33:01</t>
+          <t>18:41:36</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J362" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="K362" t="n">
         <v>361</v>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R362" t="inlineStr">
         <is>
-          <t>PANATO Cecilia</t>
-        </is>
-      </c>
-      <c r="U362" t="inlineStr">
-        <is>
-          <t>75522</t>
+          <t>SMOLDAS Michal</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>ZAPLETAL Vojtech</t>
+        </is>
+      </c>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>43186</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>43285</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -24969,7 +25289,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -24994,38 +25314,48 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>18:34:34</t>
+          <t>18:43:03</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J363" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K363" t="n">
         <v>362</v>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R363" t="inlineStr">
         <is>
-          <t>NEMCOVA Marie</t>
-        </is>
-      </c>
-      <c r="U363" t="inlineStr">
-        <is>
-          <t>78808</t>
+          <t>SKAKALA Juraj</t>
+        </is>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>GEWISSLER Matus</t>
+        </is>
+      </c>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>39248</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>39249</t>
         </is>
       </c>
     </row>
@@ -25067,48 +25397,48 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>18:40:01</t>
+          <t>18:44:34</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>CRO</t>
         </is>
       </c>
       <c r="J364" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K364" t="n">
         <v>363</v>
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R364" t="inlineStr">
         <is>
-          <t>BASSETT Kaylen</t>
+          <t>OBADIC Luka</t>
         </is>
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>BASSETT Lachlan</t>
-        </is>
-      </c>
-      <c r="U364" t="inlineStr">
-        <is>
-          <t>75376</t>
-        </is>
-      </c>
-      <c r="V364" t="inlineStr">
-        <is>
-          <t>59988</t>
+          <t>TOLIC Ivan</t>
+        </is>
+      </c>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>39639</t>
+        </is>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>39671</t>
         </is>
       </c>
     </row>
@@ -25150,48 +25480,48 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>18:41:36</t>
+          <t>18:46:03</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J365" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="K365" t="n">
         <v>364</v>
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R365" t="inlineStr">
         <is>
-          <t>SMOLDAS Michal</t>
+          <t>PAZAT Lucas</t>
         </is>
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>ZAPLETAL Vojtech</t>
-        </is>
-      </c>
-      <c r="U365" t="inlineStr">
-        <is>
-          <t>43186</t>
-        </is>
-      </c>
-      <c r="V365" t="inlineStr">
-        <is>
-          <t>43285</t>
+          <t>GOURJAULT Ancelin</t>
+        </is>
+      </c>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>63164</t>
+        </is>
+      </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>56131</t>
         </is>
       </c>
     </row>
@@ -25233,48 +25563,48 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>18:43:03</t>
+          <t>18:47:33</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J366" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K366" t="n">
         <v>365</v>
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R366" t="inlineStr">
         <is>
-          <t>SKAKALA Juraj</t>
+          <t>SUCHANEK Daniel</t>
         </is>
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>GEWISSLER Matus</t>
-        </is>
-      </c>
-      <c r="U366" t="inlineStr">
-        <is>
-          <t>39248</t>
-        </is>
-      </c>
-      <c r="V366" t="inlineStr">
-        <is>
-          <t>39249</t>
+          <t>ROLENC Ondrej</t>
+        </is>
+      </c>
+      <c r="X366" t="inlineStr">
+        <is>
+          <t>42246</t>
+        </is>
+      </c>
+      <c r="Y366" t="inlineStr">
+        <is>
+          <t>35512</t>
         </is>
       </c>
     </row>
@@ -25316,48 +25646,48 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>18:44:34</t>
+          <t>18:49:03</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>CRO</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J367" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K367" t="n">
         <v>366</v>
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R367" t="inlineStr">
         <is>
-          <t>OBADIC Luka</t>
+          <t>RYGEL Marek</t>
         </is>
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>TOLIC Ivan</t>
-        </is>
-      </c>
-      <c r="U367" t="inlineStr">
-        <is>
-          <t>39639</t>
-        </is>
-      </c>
-      <c r="V367" t="inlineStr">
-        <is>
-          <t>39671</t>
+          <t>VESELY Petr</t>
+        </is>
+      </c>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>53303</t>
+        </is>
+      </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>35511</t>
         </is>
       </c>
     </row>
@@ -25399,7 +25729,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>18:46:03</t>
+          <t>18:50:34</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -25408,39 +25738,39 @@
         </is>
       </c>
       <c r="J368" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K368" t="n">
         <v>367</v>
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R368" t="inlineStr">
         <is>
-          <t>PAZAT Lucas</t>
+          <t>LAPOINTE Louis</t>
         </is>
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>GOURJAULT Ancelin</t>
-        </is>
-      </c>
-      <c r="U368" t="inlineStr">
-        <is>
-          <t>63164</t>
-        </is>
-      </c>
-      <c r="V368" t="inlineStr">
-        <is>
-          <t>56131</t>
+          <t>DEBRAY Tony</t>
+        </is>
+      </c>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>43143</t>
+        </is>
+      </c>
+      <c r="Y368" t="inlineStr">
+        <is>
+          <t>36776</t>
         </is>
       </c>
     </row>
@@ -25482,48 +25812,48 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>18:47:33</t>
+          <t>18:52:03</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J369" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K369" t="n">
         <v>368</v>
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R369" t="inlineStr">
         <is>
-          <t>SUCHANEK Daniel</t>
+          <t>SANTAMARIA Stephane</t>
         </is>
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>ROLENC Ondrej</t>
-        </is>
-      </c>
-      <c r="U369" t="inlineStr">
-        <is>
-          <t>42246</t>
-        </is>
-      </c>
-      <c r="V369" t="inlineStr">
-        <is>
-          <t>35512</t>
+          <t>DAZEUR Quentin</t>
+        </is>
+      </c>
+      <c r="X369" t="inlineStr">
+        <is>
+          <t>36791</t>
+        </is>
+      </c>
+      <c r="Y369" t="inlineStr">
+        <is>
+          <t>43141</t>
         </is>
       </c>
     </row>
@@ -25565,55 +25895,55 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>18:49:03</t>
+          <t>18:53:31</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J370" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K370" t="n">
         <v>369</v>
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R370" t="inlineStr">
         <is>
-          <t>RYGEL Marek</t>
+          <t>HOCHSCHORNER Pavol</t>
         </is>
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>VESELY Petr</t>
-        </is>
-      </c>
-      <c r="U370" t="inlineStr">
-        <is>
-          <t>53303</t>
-        </is>
-      </c>
-      <c r="V370" t="inlineStr">
-        <is>
-          <t>35511</t>
+          <t>HOCHSCHORNER Peter</t>
+        </is>
+      </c>
+      <c r="X370" t="inlineStr">
+        <is>
+          <t>35356</t>
+        </is>
+      </c>
+      <c r="Y370" t="inlineStr">
+        <is>
+          <t>35357</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -25648,55 +25978,55 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>18:50:34</t>
+          <t>18:59:02</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J371" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K371" t="n">
         <v>370</v>
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R371" t="inlineStr">
         <is>
-          <t>LAPOINTE Louis</t>
+          <t>LUTZ Maren</t>
         </is>
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>DEBRAY Tony</t>
-        </is>
-      </c>
-      <c r="U371" t="inlineStr">
-        <is>
-          <t>43143</t>
-        </is>
-      </c>
-      <c r="V371" t="inlineStr">
-        <is>
-          <t>36776</t>
+          <t>BARM Sabrina</t>
+        </is>
+      </c>
+      <c r="X371" t="inlineStr">
+        <is>
+          <t>66240</t>
+        </is>
+      </c>
+      <c r="Y371" t="inlineStr">
+        <is>
+          <t>35175</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -25731,55 +26061,50 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>18:52:03</t>
+          <t>19:00:31</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="J372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K372" t="n">
         <v>371</v>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R372" t="inlineStr">
         <is>
-          <t>SANTAMARIA Stephane</t>
+          <t>WILSON Madison</t>
         </is>
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>DAZEUR Quentin</t>
-        </is>
-      </c>
-      <c r="U372" t="inlineStr">
-        <is>
-          <t>36791</t>
-        </is>
-      </c>
-      <c r="V372" t="inlineStr">
-        <is>
-          <t>43141</t>
+          <t>COLLIN Georgina</t>
+        </is>
+      </c>
+      <c r="Y372" t="inlineStr">
+        <is>
+          <t>60108</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -25814,48 +26139,48 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>18:53:31</t>
+          <t>19:02:03</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J373" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K373" t="n">
         <v>372</v>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R373" t="inlineStr">
         <is>
-          <t>HOCHSCHORNER Pavol</t>
+          <t>BARTH Lea Sophie</t>
         </is>
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>HOCHSCHORNER Peter</t>
-        </is>
-      </c>
-      <c r="U373" t="inlineStr">
-        <is>
-          <t>35356</t>
-        </is>
-      </c>
-      <c r="V373" t="inlineStr">
-        <is>
-          <t>35357</t>
+          <t>FEINE Constanze</t>
+        </is>
+      </c>
+      <c r="X373" t="inlineStr">
+        <is>
+          <t>64809</t>
+        </is>
+      </c>
+      <c r="Y373" t="inlineStr">
+        <is>
+          <t>93970</t>
         </is>
       </c>
     </row>
@@ -25897,48 +26222,48 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>18:59:02</t>
+          <t>19:03:34</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J374" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K374" t="n">
         <v>373</v>
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R374" t="inlineStr">
         <is>
-          <t>LUTZ Maren</t>
+          <t>KOPUNOVA Katarina</t>
         </is>
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>BARM Sabrina</t>
-        </is>
-      </c>
-      <c r="U374" t="inlineStr">
-        <is>
-          <t>66240</t>
-        </is>
-      </c>
-      <c r="V374" t="inlineStr">
-        <is>
-          <t>35175</t>
+          <t>SCHOLCZOVA Viktoria</t>
+        </is>
+      </c>
+      <c r="X374" t="inlineStr">
+        <is>
+          <t>35471</t>
+        </is>
+      </c>
+      <c r="Y374" t="inlineStr">
+        <is>
+          <t>89134</t>
         </is>
       </c>
     </row>
@@ -25980,43 +26305,48 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>19:00:31</t>
+          <t>19:05:00</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J375" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K375" t="n">
         <v>374</v>
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R375" t="inlineStr">
         <is>
-          <t>WILSON Madison</t>
+          <t>RICCIARDI Marlene</t>
         </is>
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>COLLIN Georgina</t>
-        </is>
-      </c>
-      <c r="V375" t="inlineStr">
-        <is>
-          <t>60108</t>
+          <t>PANATO Cecilia</t>
+        </is>
+      </c>
+      <c r="X375" t="inlineStr">
+        <is>
+          <t>36550</t>
+        </is>
+      </c>
+      <c r="Y375" t="inlineStr">
+        <is>
+          <t>75522</t>
         </is>
       </c>
     </row>
@@ -26058,48 +26388,48 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>19:02:03</t>
+          <t>19:06:33</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J376" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K376" t="n">
         <v>375</v>
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R376" t="inlineStr">
         <is>
-          <t>BARTH Lea Sophie</t>
+          <t>NEMCOVA Marie</t>
         </is>
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>FEINE Constanze</t>
-        </is>
-      </c>
-      <c r="U376" t="inlineStr">
-        <is>
-          <t>64809</t>
-        </is>
-      </c>
-      <c r="V376" t="inlineStr">
-        <is>
-          <t>93970</t>
+          <t>KNEBLOVA Tereza</t>
+        </is>
+      </c>
+      <c r="X376" t="inlineStr">
+        <is>
+          <t>78808</t>
+        </is>
+      </c>
+      <c r="Y376" t="inlineStr">
+        <is>
+          <t>83782</t>
         </is>
       </c>
     </row>
@@ -26141,295 +26471,46 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>19:03:34</t>
+          <t>19:08:05</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J377" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K377" t="n">
         <v>376</v>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R377" t="inlineStr">
         <is>
-          <t>KOPUNOVA Katarina</t>
+          <t>GAUBERT Elsa</t>
         </is>
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>SCHOLCZOVA Viktoria</t>
-        </is>
-      </c>
-      <c r="U377" t="inlineStr">
-        <is>
-          <t>35471</t>
-        </is>
-      </c>
-      <c r="V377" t="inlineStr">
-        <is>
-          <t>89134</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>2019-09-28</t>
-        </is>
-      </c>
-      <c r="H378" t="inlineStr">
-        <is>
-          <t>19:05:00</t>
-        </is>
-      </c>
-      <c r="I378" t="inlineStr">
-        <is>
-          <t>ITA</t>
-        </is>
-      </c>
-      <c r="J378" t="n">
-        <v>1</v>
-      </c>
-      <c r="K378" t="n">
-        <v>377</v>
-      </c>
-      <c r="M378" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N378" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R378" t="inlineStr">
-        <is>
-          <t>RICCIARDI Marlene</t>
-        </is>
-      </c>
-      <c r="S378" t="inlineStr">
-        <is>
-          <t>PANATO Cecilia</t>
-        </is>
-      </c>
-      <c r="U378" t="inlineStr">
-        <is>
-          <t>36550</t>
-        </is>
-      </c>
-      <c r="V378" t="inlineStr">
-        <is>
-          <t>75522</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G379" t="inlineStr">
-        <is>
-          <t>2019-09-28</t>
-        </is>
-      </c>
-      <c r="H379" t="inlineStr">
-        <is>
-          <t>19:06:33</t>
-        </is>
-      </c>
-      <c r="I379" t="inlineStr">
-        <is>
-          <t>CZE</t>
-        </is>
-      </c>
-      <c r="J379" t="n">
-        <v>3</v>
-      </c>
-      <c r="K379" t="n">
-        <v>378</v>
-      </c>
-      <c r="M379" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N379" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R379" t="inlineStr">
-        <is>
-          <t>NEMCOVA Marie</t>
-        </is>
-      </c>
-      <c r="S379" t="inlineStr">
-        <is>
-          <t>KNEBLOVA Tereza</t>
-        </is>
-      </c>
-      <c r="U379" t="inlineStr">
-        <is>
-          <t>78808</t>
-        </is>
-      </c>
-      <c r="V379" t="inlineStr">
-        <is>
-          <t>83782</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G380" t="inlineStr">
-        <is>
-          <t>2019-09-28</t>
-        </is>
-      </c>
-      <c r="H380" t="inlineStr">
-        <is>
-          <t>19:08:05</t>
-        </is>
-      </c>
-      <c r="I380" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="J380" t="n">
-        <v>7</v>
-      </c>
-      <c r="K380" t="n">
-        <v>379</v>
-      </c>
-      <c r="M380" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N380" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R380" t="inlineStr">
-        <is>
-          <t>GAUBERT Elsa</t>
-        </is>
-      </c>
-      <c r="S380" t="inlineStr">
-        <is>
           <t>BEZIAT Margot</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>76817</t>
         </is>
       </c>
-      <c r="V380" t="inlineStr">
+      <c r="Y377" t="inlineStr">
         <is>
           <t>86154</t>
         </is>

--- a/events/LaSeu_2019_WWC/LaSeu_2019_WWC_start.xlsx
+++ b/events/LaSeu_2019_WWC/LaSeu_2019_WWC_start.xlsx
@@ -3709,6 +3709,11 @@
           <t>35512</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>35516</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
           <t>43076</t>
